--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -35050,12 +35050,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35080,7 +35080,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35094,9 +35094,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -35107,12 +35104,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -35132,7 +35129,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -35145,42 +35142,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35212,12 +35209,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35242,7 +35239,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -35256,27 +35253,24 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -35286,12 +35280,12 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
@@ -35301,7 +35295,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -35316,7 +35310,7 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG191" t="inlineStr">
@@ -35336,17 +35330,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -35369,7 +35363,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -35382,42 +35376,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35449,12 +35443,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35504,6 +35498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35516,7 +35515,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -35526,55 +35525,55 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35606,12 +35605,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35655,22 +35654,22 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -35680,7 +35679,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -35695,7 +35694,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -35710,7 +35709,7 @@
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG193" t="inlineStr">
@@ -35730,12 +35729,12 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -35753,7 +35752,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
@@ -35763,55 +35762,55 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35843,12 +35842,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35873,7 +35872,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -35898,11 +35897,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35915,7 +35909,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -35925,55 +35919,55 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36005,12 +35999,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -36035,7 +36029,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -36054,22 +36048,22 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
@@ -36079,7 +36073,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -36094,7 +36088,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -36109,7 +36103,7 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG195" t="inlineStr">
@@ -36129,12 +36123,12 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
@@ -36152,7 +36146,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -36162,55 +36156,55 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36242,12 +36236,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36297,6 +36291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36309,7 +36308,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -36319,55 +36318,55 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36399,12 +36398,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36448,22 +36447,22 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
@@ -36473,7 +36472,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36488,7 +36487,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -36503,7 +36502,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -36523,12 +36522,12 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
@@ -36546,7 +36545,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -36556,55 +36555,55 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36636,12 +36635,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36666,7 +36665,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -36691,11 +36690,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36708,7 +36702,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -36718,55 +36712,55 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36798,12 +36792,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36828,7 +36822,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -36847,22 +36841,22 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -36872,7 +36866,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -36887,7 +36881,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -36902,7 +36896,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
@@ -36922,12 +36916,12 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -36945,7 +36939,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -36955,55 +36949,55 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37035,12 +37029,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37090,6 +37084,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -37102,7 +37101,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -37112,55 +37111,55 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37192,12 +37191,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37241,22 +37240,22 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
@@ -37266,7 +37265,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -37281,7 +37280,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -37296,7 +37295,7 @@
       </c>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG201" t="inlineStr">
@@ -37316,12 +37315,12 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -37339,7 +37338,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -37349,55 +37348,55 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37429,12 +37428,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37459,7 +37458,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -37484,11 +37483,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -37501,7 +37495,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -37511,55 +37505,55 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37591,12 +37585,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37621,7 +37615,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -37640,22 +37634,22 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
@@ -37665,7 +37659,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -37680,7 +37674,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -37695,7 +37689,7 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG203" t="inlineStr">
@@ -37715,12 +37709,12 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -37738,7 +37732,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -37748,55 +37742,55 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37828,12 +37822,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37883,6 +37877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -37895,7 +37894,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -37905,55 +37904,55 @@
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37985,12 +37984,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38034,22 +38033,22 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y205" t="inlineStr">
@@ -38059,7 +38058,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -38074,7 +38073,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -38089,7 +38088,7 @@
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG205" t="inlineStr">
@@ -38109,12 +38108,12 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM205" t="inlineStr">
@@ -38132,7 +38131,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -38142,55 +38141,55 @@
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38222,12 +38221,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38252,12 +38251,12 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N206" t="n">
@@ -38266,6 +38265,9 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -38274,68 +38276,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38362,123 +38373,505 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
         <is>
           <t>脊髓灰质炎</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="K209" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO207" t="inlineStr">
+      <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP207" t="inlineStr">
+      <c r="AP209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR207" t="inlineStr">
+      <c r="AR209" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS207" t="inlineStr"/>
-      <c r="AT207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU207" t="inlineStr">
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV207" t="inlineStr">
+      <c r="AV209" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW207" t="inlineStr">
+      <c r="AW209" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX207" t="inlineStr">
+      <c r="AX209" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY207" t="inlineStr">
+      <c r="AY209" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ207" t="inlineStr">
+      <c r="AZ209" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA207" t="inlineStr">
+      <c r="BA209" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB207" t="inlineStr">
+      <c r="BB209" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC207" t="inlineStr">
+      <c r="BC209" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -38600,7 +38993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -38610,7 +39003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -38630,7 +39023,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -38615,12 +38615,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38645,12 +38645,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -38659,6 +38659,9 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -38667,68 +38670,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38755,123 +38772,505 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
         <is>
           <t>脊髓灰质炎</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO209" t="inlineStr">
+      <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP209" t="inlineStr">
+      <c r="AP211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR209" t="inlineStr">
+      <c r="AR211" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS209" t="inlineStr"/>
-      <c r="AT209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU209" t="inlineStr">
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU211" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV209" t="inlineStr">
+      <c r="AV211" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW209" t="inlineStr">
+      <c r="AW211" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX209" t="inlineStr">
+      <c r="AX211" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY209" t="inlineStr">
+      <c r="AY211" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ209" t="inlineStr">
+      <c r="AZ211" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA209" t="inlineStr">
+      <c r="BA211" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB209" t="inlineStr">
+      <c r="BB211" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC209" t="inlineStr">
+      <c r="BC211" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -38993,7 +39392,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -39003,7 +39402,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -39023,7 +39422,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -34905,12 +34905,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34947,6 +34947,9 @@
         <v>0</v>
       </c>
       <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
         <v>0</v>
       </c>
       <c r="R189" t="n">
@@ -34983,42 +34986,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -35050,12 +35053,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35102,82 +35105,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35204,7 +35193,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -35253,98 +35242,23 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Polio</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -35438,17 +35352,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35473,7 +35387,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -35487,26 +35401,98 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Polio</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35525,7 +35511,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -35538,42 +35524,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35600,7 +35586,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -35652,98 +35638,23 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -35837,17 +35748,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35889,12 +35800,34 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -35902,6 +35835,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35909,7 +35900,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -35919,55 +35910,55 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35994,7 +35985,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -36046,98 +36037,18 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -36231,17 +36142,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36266,7 +36177,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36283,17 +36194,34 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="R196" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -36301,6 +36229,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36308,7 +36294,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -36318,55 +36304,55 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36393,7 +36379,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -36445,98 +36431,23 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -36630,17 +36541,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36682,12 +36593,34 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -36695,6 +36628,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36702,7 +36693,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -36712,55 +36703,55 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36787,7 +36778,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -36839,98 +36830,18 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -37024,17 +36935,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37059,7 +36970,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -37076,17 +36987,34 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -37094,6 +37022,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37101,7 +37087,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -37111,55 +37097,55 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37172,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -37238,98 +37224,23 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37423,17 +37334,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37475,12 +37386,34 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -37488,6 +37421,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37495,7 +37486,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -37505,55 +37496,55 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37580,7 +37571,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -37632,98 +37623,18 @@
       <c r="P203" t="n">
         <v>0</v>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -37817,17 +37728,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37852,7 +37763,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -37869,17 +37780,34 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="R204" t="n">
-        <v>0</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -37887,6 +37815,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37894,7 +37880,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -37904,55 +37890,55 @@
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37979,7 +37965,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -38031,98 +38017,23 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -38216,17 +38127,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38268,12 +38179,34 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -38281,6 +38214,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38288,7 +38279,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -38298,55 +38289,55 @@
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38373,7 +38364,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -38425,98 +38416,18 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -38610,17 +38521,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38645,7 +38556,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -38662,17 +38573,34 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -38680,6 +38608,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38687,7 +38673,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
@@ -38697,55 +38683,55 @@
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38772,7 +38758,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -38824,98 +38810,23 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -39009,17 +38920,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -39044,12 +38955,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -39058,76 +38969,168 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39159,118 +39162,657 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>脊髓灰质炎</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N211" t="n">
-        <v>0</v>
-      </c>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO211" t="inlineStr">
+      <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP211" t="inlineStr">
+      <c r="AP214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR211" t="inlineStr">
+      <c r="AR214" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS211" t="inlineStr"/>
-      <c r="AT211" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU211" t="inlineStr">
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV211" t="inlineStr">
+      <c r="AV214" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW211" t="inlineStr">
+      <c r="AW214" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AX214" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY211" t="inlineStr">
+      <c r="AY214" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ211" t="inlineStr">
+      <c r="AZ214" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA211" t="inlineStr">
+      <c r="BA214" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB211" t="inlineStr">
+      <c r="BB214" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC211" t="inlineStr">
+      <c r="BC214" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39392,7 +39934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -39402,7 +39944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -39422,7 +39964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -39818,6 +39818,405 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39851,7 +40250,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -39934,7 +40333,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -39944,7 +40343,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -39964,7 +40363,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -40217,6 +40217,400 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40333,7 +40727,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -40343,7 +40737,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -40363,7 +40757,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21756,7 +21756,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32324,7 +32324,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35053,12 +35053,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35131,42 +35131,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35198,12 +35198,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35250,82 +35250,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35352,7 +35338,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -35401,98 +35387,23 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_POLIO</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Polio</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35586,17 +35497,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35621,7 +35532,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35635,26 +35546,98 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Polio</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -35673,7 +35656,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -35686,42 +35669,42 @@
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35748,7 +35731,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -35800,98 +35783,23 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -35985,17 +35893,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -36037,12 +35945,34 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -36050,6 +35980,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36057,7 +36045,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -36067,55 +36055,55 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36142,7 +36130,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -36194,98 +36182,18 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36379,17 +36287,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36414,7 +36322,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -36431,17 +36339,34 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36449,6 +36374,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36456,7 +36439,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -36466,55 +36449,55 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36541,7 +36524,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36593,98 +36576,23 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -36778,17 +36686,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36830,12 +36738,34 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -36843,6 +36773,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36850,7 +36838,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -36860,55 +36848,55 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36923,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -36987,98 +36975,18 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -37172,17 +37080,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37207,7 +37115,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -37224,17 +37132,34 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -37242,6 +37167,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37249,7 +37232,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -37259,55 +37242,55 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37334,7 +37317,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -37386,98 +37369,23 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -37571,17 +37479,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37623,12 +37531,34 @@
       <c r="P203" t="n">
         <v>0</v>
       </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -37636,6 +37566,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37643,7 +37631,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -37653,55 +37641,55 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37716,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -37780,98 +37768,18 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -37965,17 +37873,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38000,7 +37908,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -38017,17 +37925,34 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -38035,6 +37960,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38042,7 +38025,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -38052,55 +38035,55 @@
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38110,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -38179,98 +38162,23 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -38364,17 +38272,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38416,12 +38324,34 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -38429,6 +38359,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38436,7 +38424,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -38446,55 +38434,55 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38521,7 +38509,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -38573,98 +38561,18 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -38758,17 +38666,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38793,7 +38701,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -38810,17 +38718,34 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -38828,6 +38753,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38835,7 +38818,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -38845,55 +38828,55 @@
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38920,7 +38903,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -38972,98 +38955,23 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -39157,17 +39065,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39209,12 +39117,34 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -39222,6 +39152,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -39229,7 +39217,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -39239,55 +39227,55 @@
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39314,7 +39302,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -39366,98 +39354,18 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -39551,17 +39459,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -39586,12 +39494,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -39600,76 +39508,168 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39701,12 +39701,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39779,42 +39779,42 @@
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39846,12 +39846,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -39890,9 +39890,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -39901,82 +39898,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40003,7 +39986,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -40055,98 +40038,23 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Acute poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -40240,17 +40148,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -40292,12 +40200,34 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="R217" t="n">
-        <v>0</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -40305,6 +40235,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40312,7 +40300,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
@@ -40322,55 +40310,55 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40397,7 +40385,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -40449,98 +40437,18 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R218" t="n">
+        <v>0</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN218" t="b">
-        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -40606,6 +40514,1036 @@
         </is>
       </c>
       <c r="BC218" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -40644,7 +41582,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -40727,7 +41665,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -40737,7 +41675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -40757,7 +41695,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -52469,6 +52469,944 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52502,7 +53440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -52585,7 +53523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -52595,7 +53533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -52615,7 +53553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2619,6 +2669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2764,6 +2819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6477,6 +6537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6622,6 +6687,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6767,6 +6837,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6912,6 +6987,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7057,6 +7137,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7202,6 +7287,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7347,6 +7437,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7492,6 +7587,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7637,6 +7737,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7785,6 +7890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8320,6 +8430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8864,6 +8979,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12178,6 +12298,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12323,6 +12448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12613,6 +12748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12758,6 +12898,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12903,6 +13048,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13048,6 +13198,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13193,6 +13348,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13338,6 +13498,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13486,6 +13651,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13631,6 +13801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14175,6 +14350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18279,6 +18459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18424,6 +18609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18569,6 +18759,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18714,6 +18909,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18859,6 +19059,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19004,6 +19209,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19149,6 +19359,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19294,6 +19509,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19439,6 +19659,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19587,6 +19812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19732,6 +19962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19877,6 +20112,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23587,6 +23827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23732,6 +23977,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23877,6 +24127,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24022,6 +24277,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24167,6 +24427,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24312,6 +24577,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24457,6 +24727,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24602,6 +24877,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24747,6 +25027,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24895,6 +25180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25820,6 +26110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25965,6 +26260,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30468,6 +30768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30613,6 +30918,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30758,6 +31068,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30903,6 +31218,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31048,6 +31368,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31193,6 +31518,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31338,6 +31668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31483,6 +31818,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31628,6 +31968,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31776,6 +32121,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35041,6 +35391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35186,6 +35541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38896,6 +39256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39041,6 +39406,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39186,6 +39556,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39331,6 +39706,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39476,6 +39856,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39621,6 +40006,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39766,6 +40156,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39911,6 +40306,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40056,6 +40456,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40204,6 +40609,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43859,6 +44269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44004,6 +44419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47714,6 +48134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47859,6 +48284,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48004,6 +48434,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48149,6 +48584,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48294,6 +48734,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48439,6 +48884,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48584,6 +49034,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48729,6 +49184,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48874,6 +49334,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49022,6 +49487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51897,6 +52367,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52042,6 +52517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56545,6 +57025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56690,6 +57175,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56835,6 +57325,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56980,6 +57475,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57125,6 +57625,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57270,6 +57775,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57415,6 +57925,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57560,6 +58075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57705,6 +58225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57850,6 +58375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57943,12 +58473,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -57973,7 +58503,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -57987,9 +58517,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="P320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -58000,12 +58527,12 @@
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -58025,7 +58552,7 @@
       </c>
       <c r="AS320" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT320" t="n">
@@ -58038,42 +58565,42 @@
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -58105,12 +58632,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -58135,7 +58662,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -58149,27 +58676,24 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="P321" t="n">
-        <v>0</v>
-      </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X321" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="Y321" t="inlineStr">
@@ -58179,12 +58703,12 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
@@ -58194,7 +58718,7 @@
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD321" t="inlineStr">
@@ -58209,7 +58733,7 @@
       </c>
       <c r="AF321" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG321" t="inlineStr">
@@ -58229,17 +58753,17 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM polio disease category.</t>
         </is>
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -58262,7 +58786,7 @@
       </c>
       <c r="AS321" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_POLIO</t>
         </is>
       </c>
       <c r="AT321" t="n">
@@ -58275,42 +58799,42 @@
       </c>
       <c r="AV321" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA321" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB321" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC321" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -58342,12 +58866,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -58397,6 +58921,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58409,7 +58938,7 @@
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ322" t="inlineStr">
@@ -58419,55 +58948,55 @@
       </c>
       <c r="AS322" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58499,12 +59028,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -58548,22 +59077,22 @@
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X323" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y323" t="inlineStr">
@@ -58573,7 +59102,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -58588,7 +59117,7 @@
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD323" t="inlineStr">
@@ -58603,7 +59132,7 @@
       </c>
       <c r="AF323" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG323" t="inlineStr">
@@ -58623,12 +59152,12 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM323" t="inlineStr">
@@ -58646,7 +59175,7 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ323" t="inlineStr">
@@ -58656,55 +59185,55 @@
       </c>
       <c r="AS323" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58736,12 +59265,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -58766,7 +59295,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -58791,11 +59320,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA324" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58808,7 +59332,7 @@
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ324" t="inlineStr">
@@ -58818,55 +59342,55 @@
       </c>
       <c r="AS324" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58898,12 +59422,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -58928,7 +59452,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -58947,22 +59471,22 @@
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X325" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y325" t="inlineStr">
@@ -58972,7 +59496,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -58987,7 +59511,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD325" t="inlineStr">
@@ -59002,7 +59526,7 @@
       </c>
       <c r="AF325" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG325" t="inlineStr">
@@ -59022,12 +59546,12 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM325" t="inlineStr">
@@ -59045,7 +59569,7 @@
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ325" t="inlineStr">
@@ -59055,55 +59579,55 @@
       </c>
       <c r="AS325" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59135,12 +59659,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -59190,6 +59714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA326" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -59202,7 +59731,7 @@
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ326" t="inlineStr">
@@ -59212,55 +59741,55 @@
       </c>
       <c r="AS326" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59292,12 +59821,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -59341,22 +59870,22 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X327" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y327" t="inlineStr">
@@ -59366,7 +59895,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -59381,7 +59910,7 @@
       </c>
       <c r="AC327" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD327" t="inlineStr">
@@ -59396,7 +59925,7 @@
       </c>
       <c r="AF327" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG327" t="inlineStr">
@@ -59416,12 +59945,12 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM327" t="inlineStr">
@@ -59439,7 +59968,7 @@
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ327" t="inlineStr">
@@ -59449,55 +59978,55 @@
       </c>
       <c r="AS327" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59529,12 +60058,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -59559,7 +60088,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -59584,11 +60113,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -59601,7 +60125,7 @@
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ328" t="inlineStr">
@@ -59611,55 +60135,55 @@
       </c>
       <c r="AS328" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV328" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC328" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59691,12 +60215,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -59721,7 +60245,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -59740,22 +60264,22 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X329" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y329" t="inlineStr">
@@ -59765,7 +60289,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -59780,7 +60304,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -59795,7 +60319,7 @@
       </c>
       <c r="AF329" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG329" t="inlineStr">
@@ -59815,12 +60339,12 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM329" t="inlineStr">
@@ -59838,7 +60362,7 @@
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ329" t="inlineStr">
@@ -59848,55 +60372,55 @@
       </c>
       <c r="AS329" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV329" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC329" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59928,12 +60452,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -59983,6 +60507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA330" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -59995,7 +60524,7 @@
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ330" t="inlineStr">
@@ -60005,55 +60534,55 @@
       </c>
       <c r="AS330" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -60085,12 +60614,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -60134,22 +60663,22 @@
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X331" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Acute poliomyelitis</t>
         </is>
       </c>
       <c r="Y331" t="inlineStr">
@@ -60159,7 +60688,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -60174,7 +60703,7 @@
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -60189,7 +60718,7 @@
       </c>
       <c r="AF331" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG331" t="inlineStr">
@@ -60209,12 +60738,12 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
         </is>
       </c>
       <c r="AM331" t="inlineStr">
@@ -60232,7 +60761,7 @@
       </c>
       <c r="AP331" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ331" t="inlineStr">
@@ -60242,55 +60771,55 @@
       </c>
       <c r="AS331" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV331" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC331" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -60322,12 +60851,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -60352,7 +60881,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -60377,11 +60906,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -60394,7 +60918,7 @@
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ332" t="inlineStr">
@@ -60404,55 +60928,55 @@
       </c>
       <c r="AS332" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV332" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC332" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -60484,12 +61008,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -60514,7 +61038,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -60533,22 +61057,22 @@
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X333" t="inlineStr">
         <is>
-          <t>Acute poliomyelitis</t>
+          <t>Poliomyelitis</t>
         </is>
       </c>
       <c r="Y333" t="inlineStr">
@@ -60558,7 +61082,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -60573,7 +61097,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
@@ -60588,7 +61112,7 @@
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG333" t="inlineStr">
@@ -60608,12 +61132,12 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
         <is>
-          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM333" t="inlineStr">
@@ -60631,7 +61155,7 @@
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ333" t="inlineStr">
@@ -60641,55 +61165,55 @@
       </c>
       <c r="AS333" t="inlineStr">
         <is>
-          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
         </is>
       </c>
       <c r="AT333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV333" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA333" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB333" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC333" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -60721,118 +61245,916 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN335" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP335" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ335" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV335" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW335" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY335" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA335" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB335" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC335" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO336" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP336" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV336" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW336" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA336" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB336" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC336" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN337" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_POLIOMYELITIS; SER_SG_HIST_POLIOMYELITIS</t>
+        </is>
+      </c>
+      <c r="AT337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV337" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW337" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX337" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY337" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA337" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB337" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC337" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
+      <c r="G338" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
         <is>
           <t>脊髓灰质炎</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="K338" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
+      <c r="L338" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr">
+      <c r="M338" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N334" t="n">
-        <v>0</v>
-      </c>
-      <c r="O334" t="n">
-        <v>0</v>
-      </c>
-      <c r="R334" t="n">
-        <v>0</v>
-      </c>
-      <c r="S334" t="inlineStr">
+      <c r="N338" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO334" t="inlineStr">
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP334" t="inlineStr">
+      <c r="AP338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR334" t="inlineStr">
+      <c r="AR338" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS334" t="inlineStr"/>
-      <c r="AT334" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU334" t="inlineStr">
+      <c r="AS338" t="inlineStr"/>
+      <c r="AT338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU338" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV334" t="inlineStr">
+      <c r="AV338" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW334" t="inlineStr">
+      <c r="AW338" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX334" t="inlineStr">
+      <c r="AX338" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY334" t="inlineStr">
+      <c r="AY338" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ334" t="inlineStr">
+      <c r="AZ338" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA334" t="inlineStr">
+      <c r="BA338" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB334" t="inlineStr">
+      <c r="BB338" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC334" t="inlineStr">
+      <c r="BC338" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -60954,7 +62276,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -60964,7 +62286,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
@@ -60984,7 +62306,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d013/2026-2029.xlsx
+++ b/diseases/d013/2026-2029.xlsx
@@ -62160,6 +62160,405 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO339" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP339" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS339" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT339" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV339" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA339" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB339" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC339" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" t="n">
+        <v>0</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>Acute poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK340" t="inlineStr">
+        <is>
+          <t>Japan NIID acute poliomyelitis notifications, distinct from AFP surveillance.</t>
+        </is>
+      </c>
+      <c r="AM340" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN340" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO340" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP340" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr">
+        <is>
+          <t>SER_JP_POLIOMYELITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT340" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV340" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY340" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA340" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB340" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC340" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -62193,7 +62592,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -62276,7 +62675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -62286,7 +62685,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11">
@@ -62306,7 +62705,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
